--- a/docs/Project_Info/Status Assumptions To Do.xlsx
+++ b/docs/Project_Info/Status Assumptions To Do.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CaliBL\docs\Project_Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A009EE90-A7B5-4AAE-ABEB-0ED26121CF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A98497-CC2C-466A-9494-258DC00281D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2562" yWindow="2562" windowWidth="17280" windowHeight="9984" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="2" r:id="rId1"/>
@@ -426,15 +426,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9.20703125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="62.89453125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.47265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="7.05078125" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.20703125" style="2"/>
+    <col min="1" max="1" width="62.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="7.08984375" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -445,7 +445,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -456,7 +456,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -467,7 +467,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -478,7 +478,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -486,10 +486,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -508,13 +508,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9.20703125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="57.3671875" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.20703125" style="1"/>
+    <col min="1" max="1" width="57.36328125" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -522,7 +522,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -530,7 +530,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -538,7 +538,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -546,20 +546,20 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -570,14 +570,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9.20703125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.83984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="70.734375" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.20703125" style="1"/>
+    <col min="1" max="1" width="8.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="70.7265625" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -593,7 +593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -601,7 +601,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
